--- a/DATA/MASTER/C11_MASTER/Preparacion_Machine_Learning/ipm/variables_machine_learning.xlsx
+++ b/DATA/MASTER/C11_MASTER/Preparacion_Machine_Learning/ipm/variables_machine_learning.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,44 +486,44 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Puntaje_Redundancia</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Puntaje_Multicolinealidad</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Importancia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Puntaje_Conocimiento_Dominio</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>% Cobertura</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Puntaje_Calidad</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Puntaje_Redundancia</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Puntaje_Multicolinealidad</t>
-        </is>
-      </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>IPML</t>
@@ -537,6 +537,11 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Estado_Final</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Justificacion</t>
         </is>
       </c>
     </row>
@@ -546,7 +551,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Precipitacion_mm</t>
+          <t>ONI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -567,11 +572,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.898</v>
+        <v>2.084</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -580,39 +585,39 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Variabilidad Climática</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
         <v>100</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
@@ -627,6 +632,11 @@
       <c r="V2" t="inlineStr">
         <is>
           <t>Seleccionada</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ONI</t>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -657,11 +667,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.265</v>
+        <v>3.619</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -670,39 +680,39 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Variabilidad Climática</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>100</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
@@ -717,6 +727,11 @@
       <c r="V3" t="inlineStr">
         <is>
           <t>Seleccionada</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
@@ -726,7 +741,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Radiacion_Solar</t>
+          <t>Precipitacion_mm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -747,11 +762,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.704</v>
+        <v>1.99</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -760,39 +775,39 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
         <v>100</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
@@ -807,6 +822,11 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>Seleccionada</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
@@ -816,7 +836,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Humedad_Relativa</t>
+          <t>Radiacion_Solar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -837,57 +857,57 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7.128</v>
+        <v>2.449</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
         <v>100</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
       <c r="S5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -897,16 +917,21 @@
       <c r="V5" t="inlineStr">
         <is>
           <t>Seleccionada</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Temp_Min_C</t>
+          <t>irca</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -927,57 +952,57 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10.573</v>
+        <v>2.144</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>3</v>
       </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
         <v>100</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
       <c r="S6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -987,16 +1012,21 @@
       <c r="V6" t="inlineStr">
         <is>
           <t>Seleccionada</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mes</t>
+          <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1017,11 +1047,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.152</v>
+        <v>2.114</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1030,63 +1060,68 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Temporal</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.667</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>63.64</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0.636</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8668</v>
+        <v>0.9636</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>Seleccionada</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Velocidad_Viento</t>
+          <t>Humedad_Relativa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1107,66 +1142,71 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.477</v>
+        <v>9.391</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.667</v>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
         <v>100</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8668</v>
+        <v>0.95</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>Seleccionada</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1216,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>irca</t>
+          <t>Temp_Min_C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1185,10 +1225,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1197,11 +1237,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>13.982</v>
+        <v>13.221</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1210,53 +1250,58 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
         <v>100</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.833</v>
-      </c>
       <c r="S9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8499</v>
+        <v>0.9</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>Seleccionada</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1311,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VolumenUtilDiarioMasa</t>
+          <t>Mes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1275,10 +1320,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1287,57 +1332,57 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>11.557</v>
+        <v>1.25</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Hidrológica</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
       <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R10" t="n">
         <v>100</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.833</v>
-      </c>
       <c r="S10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8499</v>
+        <v>0.8668</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1347,6 +1392,106 @@
       <c r="V10" t="inlineStr">
         <is>
           <t>Seleccionada</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Cumple todos los criterios del Framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Velocidad_Viento</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Numérica</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Muy Baja</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R11" t="n">
+        <v>100</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Seleccionada</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Cumple todos los criterios del Framework.</t>
         </is>
       </c>
     </row>
